--- a/artfynd/A 2025-2025 artfynd.xlsx
+++ b/artfynd/A 2025-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118195900</v>
+        <v>118194032</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dálvvadisoaajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673621</v>
+        <v>673519</v>
       </c>
       <c r="R2" t="n">
-        <v>7399712</v>
+        <v>7399817</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,12 +779,7 @@
         <v>118195912</v>
       </c>
       <c r="B3" t="n">
-        <v>90749</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,53 +873,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118195897</v>
+        <v>119318681</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673452</v>
+        <v>673522</v>
       </c>
       <c r="R4" t="n">
-        <v>7399754</v>
+        <v>7399820</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,27 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118194554</v>
+        <v>119318687</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,41 +981,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dálvaddisoaajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>673298</v>
+        <v>673378</v>
       </c>
       <c r="R5" t="n">
-        <v>7399692</v>
+        <v>7399870</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,27 +1055,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118195883</v>
+        <v>119318693</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1078,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>673315</v>
+        <v>673651</v>
       </c>
       <c r="R6" t="n">
-        <v>7399971</v>
+        <v>7399681</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,68 +1152,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118194032</v>
+        <v>119318695</v>
       </c>
       <c r="B7" t="n">
-        <v>90749</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dálvvadisoaajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>673519</v>
+        <v>673528</v>
       </c>
       <c r="R7" t="n">
-        <v>7399817</v>
+        <v>7399815</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,75 +1243,66 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118192587</v>
+        <v>119318696</v>
       </c>
       <c r="B8" t="n">
-        <v>90445</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>714</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallstocksticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Osmoporus protractus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Bondartsev</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dálvvadisoaajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>673463</v>
+        <v>673472</v>
       </c>
       <c r="R8" t="n">
-        <v>7399830</v>
+        <v>7399835</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,34 +1340,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118194337</v>
+        <v>119318697</v>
       </c>
       <c r="B9" t="n">
-        <v>79073</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,40 +1369,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dálvvadisoaajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673597</v>
+        <v>673425</v>
       </c>
       <c r="R9" t="n">
-        <v>7399733</v>
+        <v>7399875</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1488,72 +1437,69 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118195884</v>
+        <v>118192587</v>
       </c>
       <c r="B10" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>714</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallstocksticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Osmoporus protractus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dálvvadisoaajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673369</v>
+        <v>673463</v>
       </c>
       <c r="R10" t="n">
-        <v>7399863</v>
+        <v>7399830</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1591,6 +1537,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1609,15 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118195904</v>
+        <v>119318653</v>
       </c>
       <c r="B11" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,37 +1567,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673481</v>
+        <v>673361</v>
       </c>
       <c r="R11" t="n">
-        <v>7399700</v>
+        <v>7399861</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1699,27 +1641,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118195882</v>
+        <v>119318654</v>
       </c>
       <c r="B12" t="n">
-        <v>79073</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1727,37 +1664,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673597</v>
+        <v>673478</v>
       </c>
       <c r="R12" t="n">
-        <v>7399734</v>
+        <v>7399658</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1801,27 +1738,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119318668</v>
+        <v>119318660</v>
       </c>
       <c r="B13" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673620</v>
+        <v>673977</v>
       </c>
       <c r="R13" t="n">
-        <v>7399715</v>
+        <v>7399707</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,15 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119318669</v>
+        <v>119318666</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>673456</v>
+        <v>673758</v>
       </c>
       <c r="R14" t="n">
-        <v>7399839</v>
+        <v>7399669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,15 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119318610</v>
+        <v>119318668</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,21 +1955,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673351</v>
+        <v>673620</v>
       </c>
       <c r="R15" t="n">
-        <v>7399860</v>
+        <v>7399715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,37 +2041,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119318590</v>
+        <v>119318669</v>
       </c>
       <c r="B16" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,7 +2076,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>673455</v>
+        <v>673456</v>
       </c>
       <c r="R16" t="n">
         <v>7399839</v>
@@ -2221,15 +2138,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119318696</v>
+        <v>119358665</v>
       </c>
       <c r="B17" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2237,34 +2149,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dálvvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>673472</v>
+        <v>674024</v>
       </c>
       <c r="R17" t="n">
-        <v>7399835</v>
+        <v>7399768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,12 +2203,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2311,27 +2223,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Maria Brandt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119318693</v>
+        <v>118195883</v>
       </c>
       <c r="B18" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,37 +2246,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>673651</v>
+        <v>673315</v>
       </c>
       <c r="R18" t="n">
-        <v>7399681</v>
+        <v>7399971</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2413,27 +2320,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119318653</v>
+        <v>119318597</v>
       </c>
       <c r="B19" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,21 +2343,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2367,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>673361</v>
+        <v>673319</v>
       </c>
       <c r="R19" t="n">
-        <v>7399861</v>
+        <v>7399971</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,50 +2429,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119318606</v>
+        <v>119358640</v>
       </c>
       <c r="B20" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dálvvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>673536</v>
+        <v>673679</v>
       </c>
       <c r="R20" t="n">
-        <v>7399839</v>
+        <v>7399746</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,12 +2494,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2617,27 +2514,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Maria Brandt</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119318687</v>
+        <v>119318677</v>
       </c>
       <c r="B21" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2645,21 +2537,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2561,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>673378</v>
+        <v>673977</v>
       </c>
       <c r="R21" t="n">
-        <v>7399870</v>
+        <v>7399713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,37 +2623,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119318603</v>
+        <v>119318679</v>
       </c>
       <c r="B22" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2658,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>673627</v>
+        <v>673768</v>
       </c>
       <c r="R22" t="n">
-        <v>7399710</v>
+        <v>7399662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,15 +2720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119318597</v>
+        <v>119318680</v>
       </c>
       <c r="B23" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,21 +2731,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2873,10 +2755,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>673319</v>
+        <v>673758</v>
       </c>
       <c r="R23" t="n">
-        <v>7399971</v>
+        <v>7399670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2935,15 +2817,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119318713</v>
+        <v>120052050</v>
       </c>
       <c r="B24" t="n">
-        <v>77910</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2951,37 +2828,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>1588</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Askasluokta, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>673531</v>
+        <v>674030</v>
       </c>
       <c r="R24" t="n">
-        <v>7399838</v>
+        <v>7399766</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3005,12 +2882,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3025,62 +2902,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maria Brandt</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maria Brandt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119318695</v>
+        <v>119358653</v>
       </c>
       <c r="B25" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dálvvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>673528</v>
+        <v>673503</v>
       </c>
       <c r="R25" t="n">
-        <v>7399815</v>
+        <v>7399860</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,12 +2979,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3127,27 +2999,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Maria Brandt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119318640</v>
+        <v>119358672</v>
       </c>
       <c r="B26" t="n">
-        <v>5485</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,34 +3022,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101410</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dálvvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>673372</v>
+        <v>673513</v>
       </c>
       <c r="R26" t="n">
-        <v>7399864</v>
+        <v>7399847</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3209,12 +3076,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3229,27 +3096,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Jenny Hjelm Córdoba, Elin Götmark, Maria Brandt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119318605</v>
+        <v>119318590</v>
       </c>
       <c r="B27" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,21 +3119,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3143,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>673608</v>
+        <v>673455</v>
       </c>
       <c r="R27" t="n">
-        <v>7399721</v>
+        <v>7399839</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,15 +3205,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119318697</v>
+        <v>119318713</v>
       </c>
       <c r="B28" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3359,21 +3216,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3240,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>673425</v>
+        <v>673531</v>
       </c>
       <c r="R28" t="n">
-        <v>7399875</v>
+        <v>7399838</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3445,15 +3302,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119318649</v>
+        <v>118195904</v>
       </c>
       <c r="B29" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,17 +3333,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>673412</v>
+        <v>673481</v>
       </c>
       <c r="R29" t="n">
-        <v>7399835</v>
+        <v>7399700</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3535,27 +3387,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119318677</v>
+        <v>119318649</v>
       </c>
       <c r="B30" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3563,21 +3410,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3434,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>673977</v>
+        <v>673412</v>
       </c>
       <c r="R30" t="n">
-        <v>7399713</v>
+        <v>7399835</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,53 +3496,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119318660</v>
+        <v>118194554</v>
       </c>
       <c r="B31" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dálvaddisoaajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>673977</v>
+        <v>673298</v>
       </c>
       <c r="R31" t="n">
-        <v>7399707</v>
+        <v>7399692</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3739,44 +3585,39 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119318598</v>
+        <v>118195900</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3787,17 +3628,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>673660</v>
+        <v>673621</v>
       </c>
       <c r="R32" t="n">
-        <v>7399695</v>
+        <v>7399712</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3841,65 +3682,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119318681</v>
+        <v>118195897</v>
       </c>
       <c r="B33" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>65</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>673522</v>
+        <v>673452</v>
       </c>
       <c r="R33" t="n">
-        <v>7399820</v>
+        <v>7399754</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3943,27 +3779,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119358672</v>
+        <v>119318598</v>
       </c>
       <c r="B34" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3971,34 +3802,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Askasluokta, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>673513</v>
+        <v>673660</v>
       </c>
       <c r="R34" t="n">
-        <v>7399847</v>
+        <v>7399695</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4025,12 +3856,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4045,12 +3876,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Maria Brandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4060,12 +3891,7 @@
         <v>119358669</v>
       </c>
       <c r="B35" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,7 +3919,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Askasluokta, Lu lm</t>
+          <t>Dálvvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -4159,15 +3985,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119358665</v>
+        <v>119318640</v>
       </c>
       <c r="B36" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4175,34 +3996,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>101410</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Askasluokta, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674024</v>
+        <v>673372</v>
       </c>
       <c r="R36" t="n">
-        <v>7399768</v>
+        <v>7399864</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4229,12 +4050,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,27 +4070,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Maria Brandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119358653</v>
+        <v>119318610</v>
       </c>
       <c r="B37" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4277,31 +4093,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Askasluokta, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>673503</v>
+        <v>673351</v>
       </c>
       <c r="R37" t="n">
         <v>7399860</v>
@@ -4331,12 +4147,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4351,27 +4167,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Maria Brandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119358640</v>
+        <v>118195882</v>
       </c>
       <c r="B38" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4379,37 +4190,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Askasluokta, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>673679</v>
+        <v>673597</v>
       </c>
       <c r="R38" t="n">
-        <v>7399746</v>
+        <v>7399734</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4433,12 +4244,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,27 +4264,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jenny Hjelm Córdoba, Elin Götmark, Maria Brandt</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120052068</v>
+        <v>119318611</v>
       </c>
       <c r="B39" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,37 +4287,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>260591</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Askasluokta, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674006</v>
+        <v>673358</v>
       </c>
       <c r="R39" t="n">
-        <v>7399782</v>
+        <v>7400018</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4535,12 +4341,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,123 +4355,22 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Brandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Brandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>120052050</v>
-      </c>
-      <c r="B40" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1588</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Violmussling</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Trichaptum laricinum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Askasluokta, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>674030</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7399766</v>
-      </c>
-      <c r="S40" t="n">
-        <v>15</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Maria Brandt</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Maria Brandt</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2025-2025 artfynd.xlsx
+++ b/artfynd/A 2025-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118194032</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195912</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318681</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318687</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318693</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318695</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318696</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318697</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118192587</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318653</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318654</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318660</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318666</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318668</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318669</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358665</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195883</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318597</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358640</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2620,6 +2720,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318677</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2717,6 +2822,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318679</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2814,6 +2924,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318680</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2911,6 +3026,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120052050</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358653</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3105,6 +3230,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358672</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3202,6 +3332,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318590</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3299,6 +3434,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318713</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3396,6 +3536,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195904</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3493,6 +3638,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318649</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3594,6 +3744,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118194554</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3691,6 +3846,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195900</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3788,6 +3948,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195897</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3885,6 +4050,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318598</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3982,6 +4152,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119358669</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4079,6 +4254,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318640</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4176,6 +4356,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318610</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4273,6 +4458,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195882</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4371,8 +4561,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318611</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>